--- a/Datos Experimentales/Data 24030.xlsx
+++ b/Datos Experimentales/Data 24030.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36683DCC-945F-4343-8776-908A6BC7E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -984,11 +995,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1017,14 +1025,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1349,10 +1366,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B106"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1360,7 +1378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1368,7 +1386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1376,7 +1394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1384,7 +1402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1392,7 +1410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1400,7 +1418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1408,7 +1426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1416,7 +1434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1424,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1432,7 +1450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1440,7 +1458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1448,7 +1466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1456,7 +1474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1464,7 +1482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1472,7 +1490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1480,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1488,7 +1506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1496,7 +1514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1504,7 +1522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1512,7 +1530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1520,7 +1538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1528,7 +1546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1536,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1544,7 +1562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1552,7 +1570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1560,7 +1578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1568,7 +1586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1576,7 +1594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1584,7 +1602,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1592,7 +1610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1600,7 +1618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1608,7 +1626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1616,7 +1634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1624,7 +1642,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1632,7 +1650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1640,7 +1658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1648,7 +1666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1656,7 +1674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1664,7 +1682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1672,7 +1690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1680,7 +1698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1688,7 +1706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1696,7 +1714,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1704,7 +1722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1712,7 +1730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1720,7 +1738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1728,7 +1746,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1736,7 +1754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1744,7 +1762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1752,7 +1770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1760,7 +1778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1768,7 +1786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1776,7 +1794,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1784,7 +1802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1792,7 +1810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1800,7 +1818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1808,7 +1826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1816,7 +1834,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1824,7 +1842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1832,7 +1850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1840,7 +1858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1848,7 +1866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1856,7 +1874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1864,7 +1882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1872,7 +1890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1880,7 +1898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1888,7 +1906,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -1904,7 +1922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -1912,7 +1930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -1920,7 +1938,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -1928,7 +1946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -1936,7 +1954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -1944,7 +1962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -1952,7 +1970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -1960,7 +1978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -1968,7 +1986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -1976,7 +1994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -1984,7 +2002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -1992,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -2000,7 +2018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2008,7 +2026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2016,7 +2034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2024,7 +2042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2032,7 +2050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2040,7 +2058,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -2048,7 +2066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>100</v>
       </c>
@@ -2056,7 +2074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -2064,7 +2082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -2072,7 +2090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -2080,7 +2098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -2088,7 +2106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -2096,7 +2114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -2104,7 +2122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2112,7 +2130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2120,7 +2138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2128,7 +2146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2136,7 +2154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2144,7 +2162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2152,7 +2170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2160,7 +2178,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -2168,7 +2186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -2176,7 +2194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -2184,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -2192,7 +2210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -2201,27 +2219,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B106"/>
+    <ignoredError sqref="A1:B106" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>268</v>
       </c>
@@ -2242,17 +2264,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>273</v>
       </c>
@@ -2263,7 +2287,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -2274,40 +2298,40 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
       <c r="B3">
-        <v>0.4701388888888889</v>
+        <v>0.47013888888888888</v>
       </c>
       <c r="C3">
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
       <c r="B4">
-        <v>0.7201388888888889</v>
+        <v>0.72013888888888888</v>
       </c>
       <c r="C4">
         <v>19</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
       <c r="B5">
-        <v>0.9701388888888889</v>
+        <v>0.97013888888888888</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -2318,7 +2342,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>281</v>
       </c>
@@ -2329,7 +2353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>282</v>
       </c>
@@ -2340,7 +2364,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>283</v>
       </c>
@@ -2351,381 +2375,383 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>284</v>
       </c>
       <c r="B10">
-        <v>2.220138888888889</v>
+        <v>2.2201388888888891</v>
       </c>
       <c r="C10">
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>285</v>
       </c>
       <c r="B11">
-        <v>2.470138888888889</v>
+        <v>2.4701388888888891</v>
       </c>
       <c r="C11">
         <v>19</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>286</v>
       </c>
       <c r="B12">
-        <v>2.720138888888889</v>
+        <v>2.7201388888888891</v>
       </c>
       <c r="C12">
         <v>19</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>287</v>
       </c>
       <c r="B13">
-        <v>2.970138888888889</v>
+        <v>2.9701388888888891</v>
       </c>
       <c r="C13">
         <v>19</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
       <c r="B14">
-        <v>3.220138888888889</v>
+        <v>3.2201388888888891</v>
       </c>
       <c r="C14">
         <v>20.3</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
       <c r="B15">
-        <v>3.470138888888889</v>
+        <v>3.4701388888888891</v>
       </c>
       <c r="C15">
         <v>19.2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
       <c r="B16">
-        <v>3.720138888888889</v>
+        <v>3.7201388888888891</v>
       </c>
       <c r="C16">
         <v>19.5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
       <c r="B17">
-        <v>3.970138888888889</v>
+        <v>3.9701388888888891</v>
       </c>
       <c r="C17">
         <v>18.5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
       <c r="B18">
-        <v>4.220138888888889</v>
+        <v>4.2201388888888891</v>
       </c>
       <c r="C18">
         <v>19</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
       <c r="B19">
-        <v>4.470138888888889</v>
+        <v>4.4701388888888891</v>
       </c>
       <c r="C19">
         <v>19.8</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
       <c r="B20">
-        <v>4.720138888888889</v>
+        <v>4.7201388888888891</v>
       </c>
       <c r="C20">
         <v>18.5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
       <c r="B21">
-        <v>4.970138888888889</v>
+        <v>4.9701388888888891</v>
       </c>
       <c r="C21">
         <v>19.5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
       <c r="B22">
-        <v>5.220138888888889</v>
+        <v>5.2201388888888891</v>
       </c>
       <c r="C22">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
       <c r="B23">
-        <v>5.470138888888889</v>
+        <v>5.4701388888888891</v>
       </c>
       <c r="C23">
         <v>19</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
       <c r="B24">
-        <v>5.720138888888889</v>
+        <v>5.7201388888888891</v>
       </c>
       <c r="C24">
         <v>19</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
       <c r="B25">
-        <v>5.970138888888889</v>
+        <v>5.9701388888888891</v>
       </c>
       <c r="C25">
         <v>20</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>299</v>
       </c>
       <c r="B26">
-        <v>5.970138888888889</v>
+        <v>5.9701388888888891</v>
       </c>
       <c r="C26">
         <v>20</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>300</v>
       </c>
       <c r="B27">
-        <v>6.220138888888889</v>
+        <v>6.2201388888888891</v>
       </c>
       <c r="C27">
         <v>19.3</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
       <c r="B28">
-        <v>6.470138888888889</v>
+        <v>6.4701388888888891</v>
       </c>
       <c r="C28">
         <v>18.8</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
       <c r="B29">
-        <v>6.720138888888889</v>
+        <v>6.7201388888888891</v>
       </c>
       <c r="C29">
         <v>19</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>303</v>
       </c>
       <c r="B30">
-        <v>6.970138888888889</v>
+        <v>6.9701388888888891</v>
       </c>
       <c r="C30">
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>304</v>
       </c>
       <c r="B31">
-        <v>7.220138888888889</v>
+        <v>7.2201388888888891</v>
       </c>
       <c r="C31">
         <v>19.3</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>305</v>
       </c>
       <c r="B32">
-        <v>7.470138888888889</v>
+        <v>7.4701388888888891</v>
       </c>
       <c r="C32">
         <v>19.2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>306</v>
       </c>
       <c r="B33">
-        <v>7.720138888888889</v>
+        <v>7.7201388888888891</v>
       </c>
       <c r="C33">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>307</v>
       </c>
       <c r="B34">
-        <v>7.970138888888889</v>
+        <v>7.9701388888888891</v>
       </c>
       <c r="C34">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>308</v>
       </c>
       <c r="B35">
-        <v>8.220138888888888</v>
+        <v>8.2201388888888882</v>
       </c>
       <c r="C35">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>309</v>
       </c>
       <c r="B36">
-        <v>8.470138888888888</v>
+        <v>8.4701388888888882</v>
       </c>
       <c r="C36">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>310</v>
       </c>
       <c r="B37">
-        <v>8.720138888888888</v>
+        <v>8.7201388888888882</v>
       </c>
       <c r="C37">
         <v>19</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>311</v>
       </c>
       <c r="B38">
-        <v>8.970138888888888</v>
+        <v>8.9701388888888882</v>
       </c>
       <c r="C38">
-        <v>19.6</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>312</v>
       </c>
       <c r="B39">
-        <v>9.220138888888888</v>
+        <v>9.2201388888888882</v>
       </c>
       <c r="C39">
         <v>18.3</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>313</v>
       </c>
       <c r="B40">
-        <v>9.470138888888888</v>
+        <v>9.4701388888888882</v>
       </c>
       <c r="C40">
         <v>18.3</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>314</v>
       </c>
       <c r="B41">
-        <v>9.720138888888888</v>
+        <v>9.7201388888888882</v>
       </c>
       <c r="C41">
         <v>18.3</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>315</v>
       </c>
       <c r="B42">
-        <v>9.970138888888888</v>
+        <v>9.9701388888888882</v>
       </c>
       <c r="C42">
         <v>18.8</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
+    <ignoredError sqref="A1:C42" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>273</v>
       </c>
@@ -2736,7 +2762,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -2747,40 +2773,40 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
       <c r="B3">
-        <v>0.4701388888888889</v>
+        <v>0.47013888888888888</v>
       </c>
       <c r="C3">
         <v>1082</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
       <c r="B4">
-        <v>0.7201388888888889</v>
+        <v>0.72013888888888888</v>
       </c>
       <c r="C4">
         <v>1081</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
       <c r="B5">
-        <v>0.9701388888888889</v>
+        <v>0.97013888888888888</v>
       </c>
       <c r="C5">
         <v>1074</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -2791,7 +2817,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>281</v>
       </c>
@@ -2802,7 +2828,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>282</v>
       </c>
@@ -2813,7 +2839,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>283</v>
       </c>
@@ -2824,381 +2850,383 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>284</v>
       </c>
       <c r="B10">
-        <v>2.220138888888889</v>
+        <v>2.2201388888888891</v>
       </c>
       <c r="C10">
         <v>1040</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>285</v>
       </c>
       <c r="B11">
-        <v>2.470138888888889</v>
+        <v>2.4701388888888891</v>
       </c>
       <c r="C11">
         <v>1033</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>286</v>
       </c>
       <c r="B12">
-        <v>2.720138888888889</v>
+        <v>2.7201388888888891</v>
       </c>
       <c r="C12">
         <v>1028</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>287</v>
       </c>
       <c r="B13">
-        <v>2.970138888888889</v>
+        <v>2.9701388888888891</v>
       </c>
       <c r="C13">
         <v>1023</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
       <c r="B14">
-        <v>3.220138888888889</v>
+        <v>3.2201388888888891</v>
       </c>
       <c r="C14">
         <v>1021</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
       <c r="B15">
-        <v>3.470138888888889</v>
+        <v>3.4701388888888891</v>
       </c>
       <c r="C15">
         <v>1017</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
       <c r="B16">
-        <v>3.720138888888889</v>
+        <v>3.7201388888888891</v>
       </c>
       <c r="C16">
         <v>1014</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
       <c r="B17">
-        <v>3.970138888888889</v>
+        <v>3.9701388888888891</v>
       </c>
       <c r="C17">
         <v>1012</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
       <c r="B18">
-        <v>4.220138888888889</v>
+        <v>4.2201388888888891</v>
       </c>
       <c r="C18">
         <v>1010</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
       <c r="B19">
-        <v>4.470138888888889</v>
+        <v>4.4701388888888891</v>
       </c>
       <c r="C19">
         <v>1007</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
       <c r="B20">
-        <v>4.720138888888889</v>
+        <v>4.7201388888888891</v>
       </c>
       <c r="C20">
         <v>1005</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
       <c r="B21">
-        <v>4.970138888888889</v>
+        <v>4.9701388888888891</v>
       </c>
       <c r="C21">
         <v>1004</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
       <c r="B22">
-        <v>5.220138888888889</v>
+        <v>5.2201388888888891</v>
       </c>
       <c r="C22">
         <v>1004</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
       <c r="B23">
-        <v>5.470138888888889</v>
+        <v>5.4701388888888891</v>
       </c>
       <c r="C23">
         <v>1002</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
       <c r="B24">
-        <v>5.720138888888889</v>
+        <v>5.7201388888888891</v>
       </c>
       <c r="C24">
         <v>1000</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
       <c r="B25">
-        <v>5.970138888888889</v>
+        <v>5.9701388888888891</v>
       </c>
       <c r="C25">
         <v>998</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>299</v>
       </c>
       <c r="B26">
-        <v>5.970138888888889</v>
+        <v>5.9701388888888891</v>
       </c>
       <c r="C26">
         <v>998</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>300</v>
       </c>
       <c r="B27">
-        <v>6.220138888888889</v>
+        <v>6.2201388888888891</v>
       </c>
       <c r="C27">
         <v>999</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
       <c r="B28">
-        <v>6.470138888888889</v>
+        <v>6.4701388888888891</v>
       </c>
       <c r="C28">
         <v>998</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
       <c r="B29">
-        <v>6.720138888888889</v>
+        <v>6.7201388888888891</v>
       </c>
       <c r="C29">
         <v>998</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>303</v>
       </c>
       <c r="B30">
-        <v>6.970138888888889</v>
+        <v>6.9701388888888891</v>
       </c>
       <c r="C30">
         <v>996</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>304</v>
       </c>
       <c r="B31">
-        <v>7.220138888888889</v>
+        <v>7.2201388888888891</v>
       </c>
       <c r="C31">
         <v>996</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>305</v>
       </c>
       <c r="B32">
-        <v>7.470138888888889</v>
+        <v>7.4701388888888891</v>
       </c>
       <c r="C32">
         <v>995</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>306</v>
       </c>
       <c r="B33">
-        <v>7.720138888888889</v>
+        <v>7.7201388888888891</v>
       </c>
       <c r="C33">
         <v>994</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>307</v>
       </c>
       <c r="B34">
-        <v>7.970138888888889</v>
+        <v>7.9701388888888891</v>
       </c>
       <c r="C34">
         <v>994</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>308</v>
       </c>
       <c r="B35">
-        <v>8.220138888888888</v>
+        <v>8.2201388888888882</v>
       </c>
       <c r="C35">
         <v>994</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>309</v>
       </c>
       <c r="B36">
-        <v>8.470138888888888</v>
+        <v>8.4701388888888882</v>
       </c>
       <c r="C36">
         <v>994</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>310</v>
       </c>
       <c r="B37">
-        <v>8.720138888888888</v>
+        <v>8.7201388888888882</v>
       </c>
       <c r="C37">
         <v>994</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>311</v>
       </c>
       <c r="B38">
-        <v>8.970138888888888</v>
+        <v>8.9701388888888882</v>
       </c>
       <c r="C38">
         <v>994</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>312</v>
       </c>
       <c r="B39">
-        <v>9.220138888888888</v>
+        <v>9.2201388888888882</v>
       </c>
       <c r="C39">
         <v>994</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>313</v>
       </c>
       <c r="B40">
-        <v>9.470138888888888</v>
+        <v>9.4701388888888882</v>
       </c>
       <c r="C40">
         <v>994</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>314</v>
       </c>
       <c r="B41">
-        <v>9.720138888888888</v>
+        <v>9.7201388888888882</v>
       </c>
       <c r="C41">
         <v>993</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>315</v>
       </c>
       <c r="B42">
-        <v>9.970138888888888</v>
+        <v>9.9701388888888882</v>
       </c>
       <c r="C42">
         <v>993</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
+    <ignoredError sqref="A1:C42" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>273</v>
       </c>
@@ -3222,17 +3250,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CO2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3513,7 +3543,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -3704,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -3746,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="CC2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CD2">
         <v>0</v>
@@ -3774,17 +3804,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CO2"/>
+    <ignoredError sqref="A1:CO2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -3837,7 +3869,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -3866,7 +3898,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9849</v>
       </c>
@@ -3901,7 +3933,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9849</v>
       </c>
@@ -3930,7 +3962,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9849</v>
       </c>
@@ -3944,7 +3976,7 @@
         <v>167</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>163</v>
@@ -3980,7 +4012,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9849</v>
       </c>
@@ -3994,7 +4026,7 @@
         <v>167</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>163</v>
@@ -4030,7 +4062,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9849</v>
       </c>
@@ -4065,7 +4097,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9849</v>
       </c>
@@ -4112,7 +4144,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9849</v>
       </c>
@@ -4141,7 +4173,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9849</v>
       </c>
@@ -4176,7 +4208,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9849</v>
       </c>
@@ -4211,7 +4243,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9849</v>
       </c>
@@ -4247,17 +4279,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4289,7 +4323,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4321,7 +4355,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9849</v>
       </c>
@@ -4353,7 +4387,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9849</v>
       </c>
@@ -4386,27 +4420,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4438,7 +4476,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4471,17 +4509,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4498,7 +4538,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4510,27 +4550,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4580,7 +4624,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4593,7 +4637,7 @@
       <c r="D2">
         <v>6824</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.780543981484</v>
       </c>
       <c r="F2" t="s">
@@ -4624,13 +4668,13 @@
         <v>224</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9849</v>
       </c>
@@ -4643,7 +4687,7 @@
       <c r="D3">
         <v>6824</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.780543981484</v>
       </c>
       <c r="F3" t="s">
@@ -4674,13 +4718,13 @@
         <v>224</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9849</v>
       </c>
@@ -4693,7 +4737,7 @@
       <c r="D4">
         <v>6824</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.780543981484</v>
       </c>
       <c r="F4" t="s">
@@ -4730,7 +4774,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9849</v>
       </c>
@@ -4743,7 +4787,7 @@
       <c r="D5">
         <v>6824</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.780543981484</v>
       </c>
       <c r="F5" t="s">
@@ -4780,7 +4824,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9849</v>
       </c>
@@ -4793,7 +4837,7 @@
       <c r="D6">
         <v>6824</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.780543981484</v>
       </c>
       <c r="F6" t="s">
@@ -4830,7 +4874,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9849</v>
       </c>
@@ -4843,7 +4887,7 @@
       <c r="D7">
         <v>6824</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.780543981484</v>
       </c>
       <c r="F7" t="s">
@@ -4880,7 +4924,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9849</v>
       </c>
@@ -4893,7 +4937,7 @@
       <c r="D8">
         <v>6824</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.780543981484</v>
       </c>
       <c r="F8" t="s">
@@ -4930,7 +4974,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9849</v>
       </c>
@@ -4943,8 +4987,8 @@
       <c r="D9">
         <v>6891</v>
       </c>
-      <c r="E9">
-        <v>45376.659791666665</v>
+      <c r="E9" s="1">
+        <v>45373.659791666665</v>
       </c>
       <c r="F9" t="s">
         <v>123</v>
@@ -4974,13 +5018,13 @@
         <v>224</v>
       </c>
       <c r="O9">
-        <v>7.9254</v>
+        <v>7.9253999999999998</v>
       </c>
       <c r="P9" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9849</v>
       </c>
@@ -4993,8 +5037,8 @@
       <c r="D10">
         <v>6891</v>
       </c>
-      <c r="E10">
-        <v>45376.659791666665</v>
+      <c r="E10" s="1">
+        <v>45373.659791666665</v>
       </c>
       <c r="F10" t="s">
         <v>123</v>
@@ -5030,7 +5074,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9849</v>
       </c>
@@ -5043,8 +5087,8 @@
       <c r="D11">
         <v>6891</v>
       </c>
-      <c r="E11">
-        <v>45376.659791666665</v>
+      <c r="E11" s="1">
+        <v>45373.659791666665</v>
       </c>
       <c r="F11" t="s">
         <v>123</v>
@@ -5074,13 +5118,13 @@
         <v>224</v>
       </c>
       <c r="O11">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="P11" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9849</v>
       </c>
@@ -5093,8 +5137,8 @@
       <c r="D12">
         <v>6891</v>
       </c>
-      <c r="E12">
-        <v>45376.659791666665</v>
+      <c r="E12" s="1">
+        <v>45373.659791666665</v>
       </c>
       <c r="F12" t="s">
         <v>123</v>
@@ -5130,7 +5174,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9849</v>
       </c>
@@ -5143,8 +5187,8 @@
       <c r="D13">
         <v>6891</v>
       </c>
-      <c r="E13">
-        <v>45376.659791666665</v>
+      <c r="E13" s="1">
+        <v>45373.659791666665</v>
       </c>
       <c r="F13" t="s">
         <v>123</v>
@@ -5180,7 +5224,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9849</v>
       </c>
@@ -5193,8 +5237,8 @@
       <c r="D14">
         <v>6891</v>
       </c>
-      <c r="E14">
-        <v>45376.659791666665</v>
+      <c r="E14" s="1">
+        <v>45373.659791666665</v>
       </c>
       <c r="F14" t="s">
         <v>123</v>
@@ -5224,13 +5268,13 @@
         <v>224</v>
       </c>
       <c r="O14">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="P14" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9849</v>
       </c>
@@ -5243,8 +5287,8 @@
       <c r="D15">
         <v>6891</v>
       </c>
-      <c r="E15">
-        <v>45376.659791666665</v>
+      <c r="E15" s="1">
+        <v>45373.659791666665</v>
       </c>
       <c r="F15" t="s">
         <v>123</v>
@@ -5280,7 +5324,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9849</v>
       </c>
@@ -5293,8 +5337,8 @@
       <c r="D16">
         <v>7094</v>
       </c>
-      <c r="E16">
-        <v>45383.61971064815</v>
+      <c r="E16" s="1">
+        <v>45383.619710648149</v>
       </c>
       <c r="F16" t="s">
         <v>123</v>
@@ -5330,7 +5374,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9849</v>
       </c>
@@ -5343,8 +5387,8 @@
       <c r="D17">
         <v>7102</v>
       </c>
-      <c r="E17">
-        <v>45383.62428240741</v>
+      <c r="E17" s="1">
+        <v>45383.624282407407</v>
       </c>
       <c r="F17" t="s">
         <v>123</v>
@@ -5380,7 +5424,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9849</v>
       </c>
@@ -5393,8 +5437,8 @@
       <c r="D18">
         <v>7176</v>
       </c>
-      <c r="E18">
-        <v>45384.86753472222</v>
+      <c r="E18" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F18" t="s">
         <v>123</v>
@@ -5430,7 +5474,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9849</v>
       </c>
@@ -5443,8 +5487,8 @@
       <c r="D19">
         <v>7176</v>
       </c>
-      <c r="E19">
-        <v>45384.86753472222</v>
+      <c r="E19" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F19" t="s">
         <v>123</v>
@@ -5480,7 +5524,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9849</v>
       </c>
@@ -5493,8 +5537,8 @@
       <c r="D20">
         <v>7176</v>
       </c>
-      <c r="E20">
-        <v>45384.86753472222</v>
+      <c r="E20" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F20" t="s">
         <v>123</v>
@@ -5530,7 +5574,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9849</v>
       </c>
@@ -5543,8 +5587,8 @@
       <c r="D21">
         <v>7176</v>
       </c>
-      <c r="E21">
-        <v>45384.86753472222</v>
+      <c r="E21" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F21" t="s">
         <v>123</v>
@@ -5580,7 +5624,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9849</v>
       </c>
@@ -5593,8 +5637,8 @@
       <c r="D22">
         <v>7176</v>
       </c>
-      <c r="E22">
-        <v>45384.86753472222</v>
+      <c r="E22" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F22" t="s">
         <v>123</v>
@@ -5624,13 +5668,13 @@
         <v>224</v>
       </c>
       <c r="O22">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="P22" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9849</v>
       </c>
@@ -5643,8 +5687,8 @@
       <c r="D23">
         <v>7176</v>
       </c>
-      <c r="E23">
-        <v>45384.86753472222</v>
+      <c r="E23" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F23" t="s">
         <v>123</v>
@@ -5674,13 +5718,13 @@
         <v>224</v>
       </c>
       <c r="O23">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="P23" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9849</v>
       </c>
@@ -5693,8 +5737,8 @@
       <c r="D24">
         <v>7176</v>
       </c>
-      <c r="E24">
-        <v>45384.86753472222</v>
+      <c r="E24" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F24" t="s">
         <v>123</v>
@@ -5730,7 +5774,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9849</v>
       </c>
@@ -5743,8 +5787,8 @@
       <c r="D25">
         <v>7176</v>
       </c>
-      <c r="E25">
-        <v>45384.86753472222</v>
+      <c r="E25" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F25" t="s">
         <v>123</v>
@@ -5780,7 +5824,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9849</v>
       </c>
@@ -5793,8 +5837,8 @@
       <c r="D26">
         <v>7176</v>
       </c>
-      <c r="E26">
-        <v>45384.86753472222</v>
+      <c r="E26" s="1">
+        <v>45384.867534722223</v>
       </c>
       <c r="F26" t="s">
         <v>123</v>
@@ -5830,7 +5874,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9849</v>
       </c>
@@ -5843,8 +5887,8 @@
       <c r="D27">
         <v>7421</v>
       </c>
-      <c r="E27">
-        <v>45391.68587962963</v>
+      <c r="E27" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F27" t="s">
         <v>123</v>
@@ -5880,7 +5924,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9849</v>
       </c>
@@ -5893,8 +5937,8 @@
       <c r="D28">
         <v>7421</v>
       </c>
-      <c r="E28">
-        <v>45391.68587962963</v>
+      <c r="E28" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F28" t="s">
         <v>123</v>
@@ -5930,7 +5974,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9849</v>
       </c>
@@ -5943,8 +5987,8 @@
       <c r="D29">
         <v>7421</v>
       </c>
-      <c r="E29">
-        <v>45391.68587962963</v>
+      <c r="E29" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F29" t="s">
         <v>123</v>
@@ -5980,7 +6024,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9849</v>
       </c>
@@ -5993,8 +6037,8 @@
       <c r="D30">
         <v>7421</v>
       </c>
-      <c r="E30">
-        <v>45391.68587962963</v>
+      <c r="E30" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F30" t="s">
         <v>123</v>
@@ -6030,7 +6074,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9849</v>
       </c>
@@ -6043,8 +6087,8 @@
       <c r="D31">
         <v>7421</v>
       </c>
-      <c r="E31">
-        <v>45391.68587962963</v>
+      <c r="E31" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F31" t="s">
         <v>123</v>
@@ -6080,7 +6124,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9849</v>
       </c>
@@ -6093,8 +6137,8 @@
       <c r="D32">
         <v>7421</v>
       </c>
-      <c r="E32">
-        <v>45391.68587962963</v>
+      <c r="E32" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F32" t="s">
         <v>123</v>
@@ -6130,7 +6174,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9849</v>
       </c>
@@ -6143,8 +6187,8 @@
       <c r="D33">
         <v>7421</v>
       </c>
-      <c r="E33">
-        <v>45391.68587962963</v>
+      <c r="E33" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F33" t="s">
         <v>123</v>
@@ -6180,7 +6224,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9849</v>
       </c>
@@ -6193,8 +6237,8 @@
       <c r="D34">
         <v>7421</v>
       </c>
-      <c r="E34">
-        <v>45391.68587962963</v>
+      <c r="E34" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F34" t="s">
         <v>123</v>
@@ -6230,7 +6274,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9849</v>
       </c>
@@ -6243,8 +6287,8 @@
       <c r="D35">
         <v>7421</v>
       </c>
-      <c r="E35">
-        <v>45391.68587962963</v>
+      <c r="E35" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F35" t="s">
         <v>123</v>
@@ -6280,7 +6324,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9849</v>
       </c>
@@ -6293,8 +6337,8 @@
       <c r="D36">
         <v>7421</v>
       </c>
-      <c r="E36">
-        <v>45391.68587962963</v>
+      <c r="E36" s="1">
+        <v>45391.685879629629</v>
       </c>
       <c r="F36" t="s">
         <v>123</v>
@@ -6331,8 +6375,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P36"/>
+    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24030.xlsx
+++ b/Datos Experimentales/Data 24030.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36683DCC-945F-4343-8776-908A6BC7E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9957F67B-FC2C-472F-916E-47BECC8E5D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="320">
   <si>
     <t>parametro</t>
   </si>
@@ -990,6 +990,9 @@
   </si>
   <si>
     <t>volumen</t>
+  </si>
+  <si>
+    <t>4. Descube</t>
   </si>
 </sst>
 </file>
@@ -1368,9 +1371,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1378,7 +1381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1402,7 +1405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1410,7 +1413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1418,7 +1421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1426,7 +1429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1434,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1442,7 +1445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1450,7 +1453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1458,7 +1461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1466,7 +1469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1474,7 +1477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1490,7 +1493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1498,7 +1501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1514,7 +1517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1522,7 +1525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1530,7 +1533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1538,7 +1541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1546,7 +1549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1562,7 +1565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1570,7 +1573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1578,7 +1581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1586,7 +1589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1594,7 +1597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1602,7 +1605,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1610,7 +1613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1618,7 +1621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1626,7 +1629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1634,7 +1637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1642,7 +1645,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1650,7 +1653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1658,7 +1661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1666,7 +1669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1674,7 +1677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1690,7 +1693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1698,7 +1701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1706,7 +1709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1714,7 +1717,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1722,7 +1725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1730,7 +1733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1738,7 +1741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1746,7 +1749,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1770,7 +1773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1786,7 +1789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1802,7 +1805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1810,7 +1813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1818,7 +1821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1826,7 +1829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1834,7 +1837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1842,7 +1845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1850,7 +1853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1858,7 +1861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1866,7 +1869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1874,7 +1877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1882,7 +1885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1890,7 +1893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1898,7 +1901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1906,7 +1909,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1914,7 +1917,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -1922,7 +1925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -1930,7 +1933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -1938,7 +1941,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -1946,7 +1949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -1962,7 +1965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -1970,7 +1973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -1986,7 +1989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -1994,7 +1997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -2002,7 +2005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2026,7 +2029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2034,7 +2037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2042,7 +2045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2050,7 +2053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2058,7 +2061,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -2066,7 +2069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>100</v>
       </c>
@@ -2074,7 +2077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -2082,7 +2085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -2090,7 +2093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -2106,7 +2109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -2122,7 +2125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2130,7 +2133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2138,7 +2141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2146,7 +2149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2154,7 +2157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2170,7 +2173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2178,7 +2181,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -2186,7 +2189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -2194,7 +2197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -2202,7 +2205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -2210,7 +2213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -2229,7 +2232,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2241,9 +2244,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>268</v>
       </c>
@@ -2274,9 +2277,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>273</v>
       </c>
@@ -2287,7 +2290,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -2309,7 +2312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -2320,7 +2323,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -2331,7 +2334,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -2342,7 +2345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>281</v>
       </c>
@@ -2353,7 +2356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>282</v>
       </c>
@@ -2364,7 +2367,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>283</v>
       </c>
@@ -2375,7 +2378,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>284</v>
       </c>
@@ -2386,7 +2389,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>285</v>
       </c>
@@ -2397,7 +2400,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>286</v>
       </c>
@@ -2408,7 +2411,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>287</v>
       </c>
@@ -2419,7 +2422,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
@@ -2430,7 +2433,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -2441,7 +2444,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
@@ -2452,7 +2455,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
@@ -2463,7 +2466,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
@@ -2474,7 +2477,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -2485,7 +2488,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
@@ -2496,7 +2499,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
@@ -2507,7 +2510,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
@@ -2518,7 +2521,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
@@ -2529,7 +2532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
@@ -2540,7 +2543,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
@@ -2551,7 +2554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>299</v>
       </c>
@@ -2562,7 +2565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>300</v>
       </c>
@@ -2573,7 +2576,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
@@ -2584,7 +2587,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
@@ -2595,7 +2598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>303</v>
       </c>
@@ -2606,7 +2609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>304</v>
       </c>
@@ -2617,7 +2620,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>305</v>
       </c>
@@ -2628,7 +2631,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>306</v>
       </c>
@@ -2639,7 +2642,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>307</v>
       </c>
@@ -2650,7 +2653,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>308</v>
       </c>
@@ -2661,7 +2664,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>309</v>
       </c>
@@ -2672,7 +2675,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>310</v>
       </c>
@@ -2683,7 +2686,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>311</v>
       </c>
@@ -2694,7 +2697,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>312</v>
       </c>
@@ -2705,7 +2708,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>313</v>
       </c>
@@ -2716,7 +2719,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>314</v>
       </c>
@@ -2727,7 +2730,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>315</v>
       </c>
@@ -2749,9 +2752,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>273</v>
       </c>
@@ -2762,7 +2765,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -2773,7 +2776,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -2784,7 +2787,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -2795,7 +2798,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -2806,7 +2809,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -2817,7 +2820,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>281</v>
       </c>
@@ -2828,7 +2831,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>282</v>
       </c>
@@ -2839,7 +2842,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>283</v>
       </c>
@@ -2850,7 +2853,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>284</v>
       </c>
@@ -2861,7 +2864,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>285</v>
       </c>
@@ -2872,7 +2875,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>286</v>
       </c>
@@ -2883,7 +2886,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>287</v>
       </c>
@@ -2894,7 +2897,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
@@ -2905,7 +2908,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -2916,7 +2919,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
@@ -2927,7 +2930,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
@@ -2938,7 +2941,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
@@ -2949,7 +2952,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
@@ -2971,7 +2974,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
@@ -2982,7 +2985,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
@@ -2993,7 +2996,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
@@ -3004,7 +3007,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
@@ -3015,7 +3018,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
@@ -3026,7 +3029,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>299</v>
       </c>
@@ -3037,7 +3040,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>300</v>
       </c>
@@ -3048,7 +3051,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
@@ -3059,7 +3062,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
@@ -3070,7 +3073,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>303</v>
       </c>
@@ -3081,7 +3084,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>304</v>
       </c>
@@ -3092,7 +3095,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>305</v>
       </c>
@@ -3103,7 +3106,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>306</v>
       </c>
@@ -3114,7 +3117,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>307</v>
       </c>
@@ -3125,7 +3128,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>308</v>
       </c>
@@ -3136,7 +3139,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>309</v>
       </c>
@@ -3147,7 +3150,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>310</v>
       </c>
@@ -3158,7 +3161,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>311</v>
       </c>
@@ -3169,7 +3172,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>312</v>
       </c>
@@ -3180,7 +3183,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>313</v>
       </c>
@@ -3191,7 +3194,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>314</v>
       </c>
@@ -3202,7 +3205,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>315</v>
       </c>
@@ -3224,9 +3227,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>273</v>
       </c>
@@ -3260,9 +3263,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CO2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:93" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3543,7 +3546,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:93" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -3814,9 +3817,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -3869,7 +3872,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -3898,7 +3901,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9849</v>
       </c>
@@ -3933,7 +3936,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9849</v>
       </c>
@@ -3962,7 +3965,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9849</v>
       </c>
@@ -4012,7 +4015,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9849</v>
       </c>
@@ -4062,7 +4065,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9849</v>
       </c>
@@ -4097,7 +4100,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9849</v>
       </c>
@@ -4144,7 +4147,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9849</v>
       </c>
@@ -4173,7 +4176,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9849</v>
       </c>
@@ -4208,7 +4211,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9849</v>
       </c>
@@ -4243,7 +4246,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9849</v>
       </c>
@@ -4289,9 +4292,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4323,7 +4326,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4355,7 +4358,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9849</v>
       </c>
@@ -4387,7 +4390,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9849</v>
       </c>
@@ -4430,7 +4433,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4442,9 +4445,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4476,7 +4479,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4519,9 +4522,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4538,7 +4541,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4560,7 +4563,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4572,9 +4575,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4624,7 +4627,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9849</v>
       </c>
@@ -4674,7 +4677,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9849</v>
       </c>
@@ -4724,7 +4727,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9849</v>
       </c>
@@ -4774,7 +4777,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9849</v>
       </c>
@@ -4824,7 +4827,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9849</v>
       </c>
@@ -4874,7 +4877,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9849</v>
       </c>
@@ -4924,7 +4927,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9849</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9849</v>
       </c>
@@ -5024,7 +5027,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9849</v>
       </c>
@@ -5074,7 +5077,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9849</v>
       </c>
@@ -5124,7 +5127,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9849</v>
       </c>
@@ -5174,7 +5177,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9849</v>
       </c>
@@ -5224,7 +5227,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9849</v>
       </c>
@@ -5274,7 +5277,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9849</v>
       </c>
@@ -5324,7 +5327,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9849</v>
       </c>
@@ -5374,7 +5377,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9849</v>
       </c>
@@ -5424,7 +5427,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9849</v>
       </c>
@@ -5474,7 +5477,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9849</v>
       </c>
@@ -5524,7 +5527,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9849</v>
       </c>
@@ -5574,7 +5577,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9849</v>
       </c>
@@ -5624,7 +5627,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9849</v>
       </c>
@@ -5674,7 +5677,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9849</v>
       </c>
@@ -5724,7 +5727,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9849</v>
       </c>
@@ -5774,7 +5777,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9849</v>
       </c>
@@ -5824,7 +5827,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9849</v>
       </c>
@@ -5874,7 +5877,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9849</v>
       </c>
@@ -5903,7 +5906,7 @@
         <v>232</v>
       </c>
       <c r="J27" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K27" t="s">
         <v>234</v>
@@ -5924,7 +5927,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9849</v>
       </c>
@@ -5953,7 +5956,7 @@
         <v>232</v>
       </c>
       <c r="J28" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K28" t="s">
         <v>248</v>
@@ -5974,7 +5977,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9849</v>
       </c>
@@ -6003,7 +6006,7 @@
         <v>232</v>
       </c>
       <c r="J29" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K29" t="s">
         <v>250</v>
@@ -6024,7 +6027,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9849</v>
       </c>
@@ -6053,7 +6056,7 @@
         <v>232</v>
       </c>
       <c r="J30" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K30" t="s">
         <v>244</v>
@@ -6074,7 +6077,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9849</v>
       </c>
@@ -6103,7 +6106,7 @@
         <v>232</v>
       </c>
       <c r="J31" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K31" t="s">
         <v>253</v>
@@ -6124,7 +6127,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9849</v>
       </c>
@@ -6153,7 +6156,7 @@
         <v>232</v>
       </c>
       <c r="J32" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K32" t="s">
         <v>264</v>
@@ -6174,7 +6177,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9849</v>
       </c>
@@ -6203,7 +6206,7 @@
         <v>232</v>
       </c>
       <c r="J33" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K33" t="s">
         <v>255</v>
@@ -6224,7 +6227,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9849</v>
       </c>
@@ -6253,7 +6256,7 @@
         <v>232</v>
       </c>
       <c r="J34" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K34" t="s">
         <v>228</v>
@@ -6274,7 +6277,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9849</v>
       </c>
@@ -6303,7 +6306,7 @@
         <v>232</v>
       </c>
       <c r="J35" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K35" t="s">
         <v>239</v>
@@ -6324,7 +6327,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9849</v>
       </c>
@@ -6353,7 +6356,7 @@
         <v>232</v>
       </c>
       <c r="J36" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="K36" t="s">
         <v>241</v>
@@ -6377,7 +6380,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P8 A16:P26 A9:D9 F9:P9 A10:D15 F10:P15 A27:I36 K27:P36" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24030.xlsx
+++ b/Datos Experimentales/Data 24030.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9957F67B-FC2C-472F-916E-47BECC8E5D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDBEDE3D-B829-4E1B-BB5D-1B8D7E5E6FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
@@ -4050,7 +4050,7 @@
         <v>124</v>
       </c>
       <c r="L6">
-        <v>1087</v>
+        <v>1070</v>
       </c>
       <c r="M6" t="s">
         <v>5</v>
@@ -4284,7 +4284,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q5 A7:Q12 A6:K6 M6:Q6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4381,7 +4381,7 @@
         <v>195</v>
       </c>
       <c r="H3">
-        <v>1087</v>
+        <v>1070</v>
       </c>
       <c r="I3">
         <v>45373</v>
@@ -4413,7 +4413,7 @@
         <v>193</v>
       </c>
       <c r="H4">
-        <v>1087</v>
+        <v>1070</v>
       </c>
       <c r="I4">
         <v>45373</v>
@@ -4425,7 +4425,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J2 A4:G4 A3:G3 I3:J3 I4:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
